--- a/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-organization.xlsx
+++ b/r4-core-102-Krankenanstaltennummer-identifier-is-missing-R4-HL7®-AT-Core-Organization-Profile/StructureDefinition-at-core-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T14:29:33+00:00</t>
+    <t>2024-10-30T16:15:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5604,7 +5604,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>21</v>
